--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run3/epoch_110/per_file_predictions_epoch_110.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run3/epoch_110/per_file_predictions_epoch_110.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="520">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="523">
   <si>
     <t>Filename</t>
   </si>
@@ -808,772 +808,781 @@
     <t>0,1,1,0</t>
   </si>
   <si>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
     <t>0,1,0,1</t>
   </si>
   <si>
-    <t>0.7883,0.0268,0.1290,0.0511</t>
-  </si>
-  <si>
-    <t>0.0026,0.0009,0.0002,0.9987</t>
-  </si>
-  <si>
-    <t>0.8768,0.0283,0.0349,0.0608</t>
-  </si>
-  <si>
-    <t>0.1953,0.0024,0.0048,0.9086</t>
-  </si>
-  <si>
-    <t>0.9933,0.0064,0.0009,0.0002</t>
-  </si>
-  <si>
-    <t>0.9965,0.0013,0.0003,0.0004</t>
-  </si>
-  <si>
-    <t>0.9983,0.0008,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9945,0.0030,0.0010,0.0003</t>
-  </si>
-  <si>
-    <t>0.9957,0.0036,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9806,0.0122,0.0017,0.0040</t>
-  </si>
-  <si>
-    <t>0.9948,0.0048,0.0005,0.0002</t>
-  </si>
-  <si>
-    <t>0.9935,0.0028,0.0008,0.0005</t>
-  </si>
-  <si>
-    <t>0.5562,0.1277,0.3093,0.0046</t>
-  </si>
-  <si>
-    <t>0.4119,0.0116,0.7033,0.0042</t>
-  </si>
-  <si>
-    <t>0.7214,0.0033,0.4602,0.0005</t>
-  </si>
-  <si>
-    <t>0.2516,0.0208,0.7422,0.0058</t>
-  </si>
-  <si>
-    <t>0.6354,0.0233,0.4424,0.0046</t>
-  </si>
-  <si>
-    <t>0.0467,0.9673,0.0015,0.0001</t>
-  </si>
-  <si>
-    <t>0.0670,0.9559,0.0021,0.0000</t>
-  </si>
-  <si>
-    <t>0.5121,0.5684,0.0236,0.0030</t>
-  </si>
-  <si>
-    <t>0.1776,0.9095,0.0013,0.0001</t>
-  </si>
-  <si>
-    <t>0.0081,0.9936,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.7012,0.0204,0.3079,0.0213</t>
-  </si>
-  <si>
-    <t>0.1637,0.0061,0.8529,0.0149</t>
-  </si>
-  <si>
-    <t>0.1214,0.0023,0.9198,0.0050</t>
-  </si>
-  <si>
-    <t>0.3035,0.0418,0.7037,0.0203</t>
-  </si>
-  <si>
-    <t>0.1669,0.0022,0.9116,0.0022</t>
-  </si>
-  <si>
-    <t>0.0763,0.0079,0.9301,0.0051</t>
-  </si>
-  <si>
-    <t>0.0012,0.0006,0.9967,0.0013</t>
-  </si>
-  <si>
-    <t>0.8044,0.2774,0.0098,0.0003</t>
-  </si>
-  <si>
-    <t>0.7534,0.1925,0.0701,0.0025</t>
-  </si>
-  <si>
-    <t>0.0023,0.0222,0.9932,0.0014</t>
-  </si>
-  <si>
-    <t>0.0673,0.8245,0.1033,0.0021</t>
-  </si>
-  <si>
-    <t>0.7946,0.1819,0.0486,0.0101</t>
-  </si>
-  <si>
-    <t>0.8128,0.0686,0.1275,0.0093</t>
-  </si>
-  <si>
-    <t>0.6276,0.5097,0.0092,0.0015</t>
-  </si>
-  <si>
-    <t>0.0499,0.9374,0.0718,0.0002</t>
-  </si>
-  <si>
-    <t>0.0531,0.8309,0.1809,0.0315</t>
-  </si>
-  <si>
-    <t>0.1755,0.0868,0.7944,0.0329</t>
-  </si>
-  <si>
-    <t>0.0142,0.4428,0.7812,0.0024</t>
-  </si>
-  <si>
-    <t>0.2555,0.0343,0.6450,0.0977</t>
-  </si>
-  <si>
-    <t>0.1583,0.0429,0.8131,0.0046</t>
-  </si>
-  <si>
-    <t>0.0094,0.9351,0.2078,0.0012</t>
-  </si>
-  <si>
-    <t>0.0635,0.0651,0.8977,0.0136</t>
-  </si>
-  <si>
-    <t>0.0347,0.8288,0.0227,0.7341</t>
-  </si>
-  <si>
-    <t>0.0013,0.9947,0.0081,0.0009</t>
-  </si>
-  <si>
-    <t>0.0033,0.9828,0.2110,0.0008</t>
-  </si>
-  <si>
-    <t>0.0011,0.9920,0.0798,0.0013</t>
-  </si>
-  <si>
-    <t>0.0462,0.0477,0.9254,0.0171</t>
-  </si>
-  <si>
-    <t>0.0003,0.8235,0.9805,0.0001</t>
-  </si>
-  <si>
-    <t>0.1590,0.0064,0.8812,0.0024</t>
-  </si>
-  <si>
-    <t>0.1172,0.0007,0.9528,0.0010</t>
-  </si>
-  <si>
-    <t>0.0208,0.0146,0.9676,0.0065</t>
-  </si>
-  <si>
-    <t>0.0071,0.0413,0.9834,0.0007</t>
-  </si>
-  <si>
-    <t>0.9642,0.0476,0.0039,0.0003</t>
-  </si>
-  <si>
-    <t>0.9766,0.0286,0.0027,0.0003</t>
-  </si>
-  <si>
-    <t>0.9835,0.0074,0.0032,0.0024</t>
-  </si>
-  <si>
-    <t>0.0314,0.4377,0.8737,0.0069</t>
-  </si>
-  <si>
-    <t>0.9637,0.0448,0.0049,0.0004</t>
-  </si>
-  <si>
-    <t>0.9942,0.0052,0.0005,0.0003</t>
-  </si>
-  <si>
-    <t>0.9931,0.0065,0.0010,0.0002</t>
-  </si>
-  <si>
-    <t>0.0077,0.7160,0.7639,0.0009</t>
-  </si>
-  <si>
-    <t>0.0067,0.1266,0.9710,0.0058</t>
-  </si>
-  <si>
-    <t>0.0189,0.1263,0.9251,0.0178</t>
-  </si>
-  <si>
-    <t>0.0011,0.7386,0.9537,0.0006</t>
-  </si>
-  <si>
-    <t>0.0049,0.0229,0.9857,0.0019</t>
-  </si>
-  <si>
-    <t>0.0326,0.9465,0.0372,0.0008</t>
-  </si>
-  <si>
-    <t>0.0052,0.9948,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.6135,0.0776,0.3727,0.0060</t>
-  </si>
-  <si>
-    <t>0.6405,0.2360,0.2020,0.0370</t>
-  </si>
-  <si>
-    <t>0.0377,0.0844,0.9325,0.0032</t>
-  </si>
-  <si>
-    <t>0.0013,0.8406,0.8896,0.0002</t>
-  </si>
-  <si>
-    <t>0.0007,0.9429,0.6107,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.9949,0.0776,0.0005</t>
-  </si>
-  <si>
-    <t>0.0012,0.8910,0.5117,0.0115</t>
-  </si>
-  <si>
-    <t>0.1004,0.0049,0.0531,0.8938</t>
-  </si>
-  <si>
-    <t>0.0046,0.0007,0.0020,0.9956</t>
-  </si>
-  <si>
-    <t>0.0387,0.0574,0.0050,0.9726</t>
-  </si>
-  <si>
-    <t>0.0213,0.0033,0.0003,0.9924</t>
-  </si>
-  <si>
-    <t>0.0370,0.0730,0.0101,0.9721</t>
-  </si>
-  <si>
-    <t>0.0084,0.0132,0.0005,0.9957</t>
-  </si>
-  <si>
-    <t>0.0010,0.9498,0.6737,0.0002</t>
-  </si>
-  <si>
-    <t>0.0018,0.7032,0.9503,0.0007</t>
-  </si>
-  <si>
-    <t>0.0389,0.2927,0.7729,0.0124</t>
-  </si>
-  <si>
-    <t>0.0040,0.5411,0.9255,0.0009</t>
-  </si>
-  <si>
-    <t>0.0007,0.9885,0.3309,0.0001</t>
-  </si>
-  <si>
-    <t>0.0026,0.7788,0.8424,0.0003</t>
-  </si>
-  <si>
-    <t>0.9921,0.0089,0.0010,0.0001</t>
-  </si>
-  <si>
-    <t>0.9829,0.0237,0.0012,0.0001</t>
-  </si>
-  <si>
-    <t>0.9680,0.0445,0.0039,0.0003</t>
-  </si>
-  <si>
-    <t>0.9919,0.0061,0.0010,0.0006</t>
-  </si>
-  <si>
-    <t>0.9746,0.0168,0.0076,0.0012</t>
-  </si>
-  <si>
-    <t>0.9966,0.0008,0.0002,0.0006</t>
-  </si>
-  <si>
-    <t>0.9929,0.0045,0.0007,0.0005</t>
-  </si>
-  <si>
-    <t>0.9809,0.0179,0.0030,0.0009</t>
-  </si>
-  <si>
-    <t>0.9941,0.0014,0.0006,0.0013</t>
-  </si>
-  <si>
-    <t>0.9886,0.0115,0.0015,0.0001</t>
-  </si>
-  <si>
-    <t>0.9977,0.0010,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9939,0.0043,0.0009,0.0003</t>
-  </si>
-  <si>
-    <t>0.9927,0.0026,0.0006,0.0011</t>
-  </si>
-  <si>
-    <t>0.9973,0.0018,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9967,0.0020,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.9923,0.0050,0.0014,0.0003</t>
-  </si>
-  <si>
-    <t>0.0021,0.0035,0.9341,0.1932</t>
-  </si>
-  <si>
-    <t>0.0554,0.0071,0.9557,0.0004</t>
-  </si>
-  <si>
-    <t>0.7810,0.0066,0.2383,0.0129</t>
-  </si>
-  <si>
-    <t>0.5200,0.0251,0.5145,0.0060</t>
-  </si>
-  <si>
-    <t>0.0386,0.9646,0.0030,0.0001</t>
-  </si>
-  <si>
-    <t>0.0627,0.9354,0.0124,0.0009</t>
-  </si>
-  <si>
-    <t>0.1963,0.8836,0.0016,0.0001</t>
-  </si>
-  <si>
-    <t>0.0486,0.9435,0.0124,0.0006</t>
-  </si>
-  <si>
-    <t>0.0597,0.9511,0.0081,0.0000</t>
-  </si>
-  <si>
-    <t>0.0290,0.9739,0.0023,0.0002</t>
-  </si>
-  <si>
-    <t>0.7809,0.2889,0.0116,0.0015</t>
-  </si>
-  <si>
-    <t>0.6123,0.0527,0.3961,0.0159</t>
-  </si>
-  <si>
-    <t>0.2137,0.0117,0.8293,0.0034</t>
-  </si>
-  <si>
-    <t>0.4848,0.2469,0.3211,0.0094</t>
-  </si>
-  <si>
-    <t>0.5410,0.0553,0.4365,0.0040</t>
-  </si>
-  <si>
-    <t>0.6441,0.1062,0.2860,0.0611</t>
-  </si>
-  <si>
-    <t>0.0023,0.9924,0.0076,0.0012</t>
-  </si>
-  <si>
-    <t>0.0063,0.9778,0.0103,0.0196</t>
-  </si>
-  <si>
-    <t>0.1305,0.8152,0.1078,0.0468</t>
-  </si>
-  <si>
-    <t>0.0022,0.8970,0.8758,0.0018</t>
-  </si>
-  <si>
-    <t>0.0256,0.9618,0.0503,0.0006</t>
-  </si>
-  <si>
-    <t>0.6395,0.2997,0.1011,0.0024</t>
-  </si>
-  <si>
-    <t>0.4980,0.5747,0.0292,0.0006</t>
-  </si>
-  <si>
-    <t>0.9774,0.0198,0.0019,0.0012</t>
-  </si>
-  <si>
-    <t>0.9859,0.0075,0.0016,0.0014</t>
-  </si>
-  <si>
-    <t>0.9838,0.0072,0.0041,0.0016</t>
-  </si>
-  <si>
-    <t>0.9580,0.0219,0.0217,0.0027</t>
-  </si>
-  <si>
-    <t>0.9900,0.0030,0.0006,0.0029</t>
-  </si>
-  <si>
-    <t>0.9692,0.0242,0.0067,0.0011</t>
-  </si>
-  <si>
-    <t>0.9835,0.0105,0.0024,0.0016</t>
-  </si>
-  <si>
-    <t>0.9819,0.0111,0.0043,0.0011</t>
-  </si>
-  <si>
-    <t>0.0214,0.7875,0.5987,0.0045</t>
-  </si>
-  <si>
-    <t>0.0195,0.5427,0.7763,0.0025</t>
-  </si>
-  <si>
-    <t>0.0235,0.3448,0.8553,0.0118</t>
-  </si>
-  <si>
-    <t>0.0391,0.0510,0.9294,0.0012</t>
-  </si>
-  <si>
-    <t>0.4959,0.0895,0.4762,0.0247</t>
-  </si>
-  <si>
-    <t>0.7809,0.0542,0.1876,0.0097</t>
-  </si>
-  <si>
-    <t>0.6875,0.0071,0.3899,0.0090</t>
-  </si>
-  <si>
-    <t>0.6142,0.0408,0.4326,0.0086</t>
-  </si>
-  <si>
-    <t>0.0175,0.0035,0.0009,0.9926</t>
-  </si>
-  <si>
-    <t>0.0009,0.0002,0.0002,0.9995</t>
-  </si>
-  <si>
-    <t>0.0048,0.0024,0.0047,0.9931</t>
-  </si>
-  <si>
-    <t>0.0103,0.0180,0.0007,0.9946</t>
-  </si>
-  <si>
-    <t>0.0020,0.9612,0.4584,0.0010</t>
-  </si>
-  <si>
-    <t>0.9875,0.0065,0.0024,0.0011</t>
-  </si>
-  <si>
-    <t>0.1923,0.7169,0.0786,0.0044</t>
-  </si>
-  <si>
-    <t>0.9679,0.0242,0.0067,0.0017</t>
-  </si>
-  <si>
-    <t>0.6446,0.5233,0.0053,0.0001</t>
-  </si>
-  <si>
-    <t>0.9751,0.0087,0.0043,0.0077</t>
-  </si>
-  <si>
-    <t>0.3032,0.2711,0.0375,0.6589</t>
-  </si>
-  <si>
-    <t>0.9797,0.0069,0.0013,0.0068</t>
-  </si>
-  <si>
-    <t>0.0261,0.1637,0.9029,0.0657</t>
-  </si>
-  <si>
-    <t>0.7937,0.0020,0.0331,0.1040</t>
-  </si>
-  <si>
-    <t>0.9585,0.0074,0.0126,0.0097</t>
-  </si>
-  <si>
-    <t>0.4846,0.5653,0.0532,0.0095</t>
-  </si>
-  <si>
-    <t>0.8877,0.0821,0.0267,0.0024</t>
-  </si>
-  <si>
-    <t>0.9170,0.0448,0.0299,0.0024</t>
-  </si>
-  <si>
-    <t>0.6717,0.2056,0.1587,0.0095</t>
-  </si>
-  <si>
-    <t>0.7290,0.2410,0.0593,0.0032</t>
-  </si>
-  <si>
-    <t>0.7174,0.2461,0.1022,0.0065</t>
-  </si>
-  <si>
-    <t>0.9928,0.0033,0.0013,0.0004</t>
-  </si>
-  <si>
-    <t>0.9914,0.0042,0.0005,0.0014</t>
-  </si>
-  <si>
-    <t>0.9934,0.0024,0.0009,0.0009</t>
-  </si>
-  <si>
-    <t>0.9953,0.0022,0.0006,0.0003</t>
-  </si>
-  <si>
-    <t>0.9761,0.0124,0.0082,0.0018</t>
-  </si>
-  <si>
-    <t>0.9779,0.0108,0.0022,0.0029</t>
-  </si>
-  <si>
-    <t>0.9919,0.0024,0.0007,0.0019</t>
-  </si>
-  <si>
-    <t>0.9837,0.0043,0.0034,0.0033</t>
-  </si>
-  <si>
-    <t>0.4457,0.6853,0.0076,0.0007</t>
-  </si>
-  <si>
-    <t>0.5260,0.4829,0.0317,0.0002</t>
-  </si>
-  <si>
-    <t>0.7627,0.3818,0.0055,0.0005</t>
-  </si>
-  <si>
-    <t>0.3007,0.6874,0.0915,0.0069</t>
-  </si>
-  <si>
-    <t>0.9908,0.0060,0.0012,0.0005</t>
-  </si>
-  <si>
-    <t>0.9421,0.0487,0.0128,0.0039</t>
-  </si>
-  <si>
-    <t>0.9786,0.0188,0.0042,0.0006</t>
-  </si>
-  <si>
-    <t>0.9707,0.0299,0.0057,0.0004</t>
-  </si>
-  <si>
-    <t>0.0005,0.0077,0.9975,0.0011</t>
-  </si>
-  <si>
-    <t>0.9613,0.0372,0.0087,0.0008</t>
-  </si>
-  <si>
-    <t>0.0143,0.0042,0.9808,0.0033</t>
-  </si>
-  <si>
-    <t>0.0136,0.0503,0.9613,0.0131</t>
-  </si>
-  <si>
-    <t>0.3419,0.0186,0.7040,0.0186</t>
-  </si>
-  <si>
-    <t>0.0335,0.1445,0.9162,0.0024</t>
-  </si>
-  <si>
-    <t>0.0604,0.0180,0.9351,0.0041</t>
-  </si>
-  <si>
-    <t>0.0241,0.0064,0.9787,0.0005</t>
-  </si>
-  <si>
-    <t>0.0050,0.0036,0.9903,0.0021</t>
-  </si>
-  <si>
-    <t>0.5820,0.0418,0.4049,0.0155</t>
-  </si>
-  <si>
-    <t>0.0653,0.0069,0.9418,0.0015</t>
-  </si>
-  <si>
-    <t>0.6382,0.0919,0.3036,0.0114</t>
-  </si>
-  <si>
-    <t>0.3306,0.2071,0.4658,0.0064</t>
-  </si>
-  <si>
-    <t>0.0481,0.8865,0.1903,0.0055</t>
-  </si>
-  <si>
-    <t>0.7139,0.0729,0.2472,0.0071</t>
-  </si>
-  <si>
-    <t>0.1067,0.0622,0.8142,0.0048</t>
-  </si>
-  <si>
-    <t>0.4954,0.0375,0.5187,0.0137</t>
-  </si>
-  <si>
-    <t>0.9343,0.0737,0.0095,0.0011</t>
-  </si>
-  <si>
-    <t>0.6351,0.5376,0.0066,0.0003</t>
-  </si>
-  <si>
-    <t>0.8937,0.1604,0.0077,0.0006</t>
-  </si>
-  <si>
-    <t>0.9483,0.0672,0.0074,0.0005</t>
-  </si>
-  <si>
-    <t>0.9725,0.0247,0.0089,0.0008</t>
-  </si>
-  <si>
-    <t>0.5484,0.1642,0.3695,0.0195</t>
-  </si>
-  <si>
-    <t>0.8262,0.0149,0.1915,0.0017</t>
-  </si>
-  <si>
-    <t>0.6921,0.0409,0.2393,0.0379</t>
-  </si>
-  <si>
-    <t>0.6795,0.0071,0.4152,0.0031</t>
-  </si>
-  <si>
-    <t>0.7193,0.0140,0.3365,0.0051</t>
-  </si>
-  <si>
-    <t>0.0110,0.0101,0.9765,0.0089</t>
-  </si>
-  <si>
-    <t>0.1402,0.1215,0.7292,0.0051</t>
-  </si>
-  <si>
-    <t>0.0515,0.0489,0.8995,0.0258</t>
-  </si>
-  <si>
-    <t>0.1903,0.0299,0.8145,0.0116</t>
-  </si>
-  <si>
-    <t>0.0322,0.0316,0.9573,0.0016</t>
-  </si>
-  <si>
-    <t>0.9958,0.0011,0.0001,0.0006</t>
-  </si>
-  <si>
-    <t>0.9813,0.0165,0.0023,0.0016</t>
-  </si>
-  <si>
-    <t>0.9944,0.0029,0.0002,0.0006</t>
-  </si>
-  <si>
-    <t>0.9876,0.0164,0.0011,0.0001</t>
-  </si>
-  <si>
-    <t>0.9878,0.0099,0.0019,0.0007</t>
-  </si>
-  <si>
-    <t>0.9842,0.0136,0.0020,0.0012</t>
-  </si>
-  <si>
-    <t>0.9855,0.0054,0.0005,0.0025</t>
-  </si>
-  <si>
-    <t>0.9942,0.0029,0.0014,0.0004</t>
-  </si>
-  <si>
-    <t>0.0664,0.0458,0.9237,0.0014</t>
-  </si>
-  <si>
-    <t>0.2469,0.0926,0.6549,0.0018</t>
-  </si>
-  <si>
-    <t>0.9385,0.0393,0.0109,0.0111</t>
-  </si>
-  <si>
-    <t>0.0084,0.0080,0.9879,0.0025</t>
-  </si>
-  <si>
-    <t>0.0012,0.0039,0.9914,0.0091</t>
-  </si>
-  <si>
-    <t>0.0199,0.0305,0.9689,0.0008</t>
-  </si>
-  <si>
-    <t>0.0003,0.0016,0.9983,0.0008</t>
-  </si>
-  <si>
-    <t>0.0820,0.0089,0.9326,0.0012</t>
-  </si>
-  <si>
-    <t>0.0028,0.0008,0.9941,0.0021</t>
-  </si>
-  <si>
-    <t>0.0229,0.0057,0.9747,0.0014</t>
-  </si>
-  <si>
-    <t>0.2336,0.0501,0.7454,0.0019</t>
-  </si>
-  <si>
-    <t>0.6209,0.0134,0.4570,0.0041</t>
-  </si>
-  <si>
-    <t>0.8087,0.0180,0.2114,0.0055</t>
-  </si>
-  <si>
-    <t>0.7361,0.0415,0.2161,0.0285</t>
-  </si>
-  <si>
-    <t>0.9846,0.0169,0.0011,0.0007</t>
-  </si>
-  <si>
-    <t>0.9971,0.0035,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9887,0.0117,0.0012,0.0002</t>
-  </si>
-  <si>
-    <t>0.9579,0.0534,0.0074,0.0002</t>
-  </si>
-  <si>
-    <t>0.9843,0.0025,0.0003,0.0054</t>
-  </si>
-  <si>
-    <t>0.9805,0.0244,0.0025,0.0001</t>
-  </si>
-  <si>
-    <t>0.9930,0.0034,0.0007,0.0007</t>
-  </si>
-  <si>
-    <t>0.9872,0.0138,0.0009,0.0006</t>
-  </si>
-  <si>
-    <t>0.1205,0.1383,0.6876,0.0019</t>
-  </si>
-  <si>
-    <t>0.0054,0.0809,0.9607,0.0010</t>
-  </si>
-  <si>
-    <t>0.0940,0.0340,0.8810,0.0079</t>
-  </si>
-  <si>
-    <t>0.0344,0.0980,0.8647,0.0020</t>
-  </si>
-  <si>
-    <t>0.0030,0.0049,0.9929,0.0019</t>
-  </si>
-  <si>
-    <t>0.3418,0.0725,0.6230,0.0797</t>
-  </si>
-  <si>
-    <t>0.3630,0.0080,0.7163,0.0132</t>
-  </si>
-  <si>
-    <t>0.0176,0.0272,0.9670,0.0055</t>
-  </si>
-  <si>
-    <t>0.5821,0.0019,0.0241,0.3633</t>
-  </si>
-  <si>
-    <t>0.0900,0.0279,0.0088,0.9492</t>
-  </si>
-  <si>
-    <t>0.0796,0.0696,0.0014,0.9585</t>
-  </si>
-  <si>
-    <t>0.0306,0.0003,0.0019,0.9810</t>
-  </si>
-  <si>
-    <t>0.0750,0.0021,0.0022,0.9717</t>
-  </si>
-  <si>
-    <t>0.9175,0.0163,0.0368,0.0084</t>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>0.7113,0.2808,0.0280,0.0115</t>
+  </si>
+  <si>
+    <t>0.0923,0.0742,0.0021,0.9597</t>
+  </si>
+  <si>
+    <t>0.8958,0.0558,0.0289,0.0161</t>
+  </si>
+  <si>
+    <t>0.2226,0.0182,0.0066,0.8848</t>
+  </si>
+  <si>
+    <t>0.9950,0.0032,0.0008,0.0002</t>
+  </si>
+  <si>
+    <t>0.9895,0.0081,0.0013,0.0006</t>
+  </si>
+  <si>
+    <t>0.9906,0.0051,0.0025,0.0004</t>
+  </si>
+  <si>
+    <t>0.9871,0.0071,0.0027,0.0014</t>
+  </si>
+  <si>
+    <t>0.9938,0.0057,0.0005,0.0002</t>
+  </si>
+  <si>
+    <t>0.9900,0.0139,0.0006,0.0001</t>
+  </si>
+  <si>
+    <t>0.9975,0.0027,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9965,0.0017,0.0004,0.0003</t>
+  </si>
+  <si>
+    <t>0.7124,0.0753,0.2299,0.0205</t>
+  </si>
+  <si>
+    <t>0.3646,0.0085,0.7288,0.0088</t>
+  </si>
+  <si>
+    <t>0.5030,0.0041,0.6595,0.0031</t>
+  </si>
+  <si>
+    <t>0.2398,0.0149,0.7869,0.0029</t>
+  </si>
+  <si>
+    <t>0.5908,0.0943,0.3847,0.0113</t>
+  </si>
+  <si>
+    <t>0.0093,0.9928,0.0007,0.0000</t>
+  </si>
+  <si>
+    <t>0.0023,0.9963,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.4544,0.7159,0.0037,0.0001</t>
+  </si>
+  <si>
+    <t>0.0530,0.9548,0.0003,0.0005</t>
+  </si>
+  <si>
+    <t>0.0009,0.9983,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.6874,0.0025,0.4282,0.0022</t>
+  </si>
+  <si>
+    <t>0.2400,0.0027,0.5156,0.1007</t>
+  </si>
+  <si>
+    <t>0.2127,0.0058,0.8606,0.0033</t>
+  </si>
+  <si>
+    <t>0.4187,0.0274,0.6200,0.0217</t>
+  </si>
+  <si>
+    <t>0.0224,0.0008,0.9848,0.0009</t>
+  </si>
+  <si>
+    <t>0.1286,0.0042,0.9133,0.0035</t>
+  </si>
+  <si>
+    <t>0.0136,0.0013,0.9898,0.0007</t>
+  </si>
+  <si>
+    <t>0.0929,0.8937,0.0127,0.0023</t>
+  </si>
+  <si>
+    <t>0.6758,0.2336,0.1378,0.0095</t>
+  </si>
+  <si>
+    <t>0.0017,0.0101,0.9933,0.0032</t>
+  </si>
+  <si>
+    <t>0.0214,0.9550,0.0555,0.0008</t>
+  </si>
+  <si>
+    <t>0.4464,0.6091,0.0395,0.0085</t>
+  </si>
+  <si>
+    <t>0.8226,0.1372,0.0436,0.0015</t>
+  </si>
+  <si>
+    <t>0.6876,0.3235,0.0244,0.0003</t>
+  </si>
+  <si>
+    <t>0.0756,0.8764,0.2200,0.0040</t>
+  </si>
+  <si>
+    <t>0.1825,0.4490,0.5104,0.0355</t>
+  </si>
+  <si>
+    <t>0.0679,0.1971,0.8442,0.0167</t>
+  </si>
+  <si>
+    <t>0.0135,0.5595,0.7595,0.0024</t>
+  </si>
+  <si>
+    <t>0.1724,0.0297,0.6400,0.1566</t>
+  </si>
+  <si>
+    <t>0.0372,0.2311,0.8864,0.0103</t>
+  </si>
+  <si>
+    <t>0.0044,0.9857,0.0282,0.0006</t>
+  </si>
+  <si>
+    <t>0.3497,0.0267,0.6888,0.0090</t>
+  </si>
+  <si>
+    <t>0.1309,0.6429,0.0299,0.6729</t>
+  </si>
+  <si>
+    <t>0.0008,0.9943,0.0030,0.0048</t>
+  </si>
+  <si>
+    <t>0.0127,0.9548,0.0961,0.0073</t>
+  </si>
+  <si>
+    <t>0.0008,0.9936,0.0754,0.0005</t>
+  </si>
+  <si>
+    <t>0.0053,0.6894,0.9121,0.0041</t>
+  </si>
+  <si>
+    <t>0.0062,0.8274,0.7679,0.0021</t>
+  </si>
+  <si>
+    <t>0.0589,0.0020,0.9601,0.0033</t>
+  </si>
+  <si>
+    <t>0.0407,0.0004,0.9839,0.0003</t>
+  </si>
+  <si>
+    <t>0.0027,0.0036,0.9908,0.0036</t>
+  </si>
+  <si>
+    <t>0.0025,0.0745,0.9857,0.0011</t>
+  </si>
+  <si>
+    <t>0.8888,0.2113,0.0021,0.0002</t>
+  </si>
+  <si>
+    <t>0.9831,0.0086,0.0043,0.0010</t>
+  </si>
+  <si>
+    <t>0.9664,0.0234,0.0090,0.0020</t>
+  </si>
+  <si>
+    <t>0.0015,0.0885,0.9935,0.0005</t>
+  </si>
+  <si>
+    <t>0.9881,0.0056,0.0023,0.0013</t>
+  </si>
+  <si>
+    <t>0.9912,0.0079,0.0008,0.0005</t>
+  </si>
+  <si>
+    <t>0.9833,0.0161,0.0009,0.0006</t>
+  </si>
+  <si>
+    <t>0.0093,0.7737,0.7609,0.0023</t>
+  </si>
+  <si>
+    <t>0.0079,0.0179,0.9812,0.0039</t>
+  </si>
+  <si>
+    <t>0.0057,0.1203,0.9275,0.0177</t>
+  </si>
+  <si>
+    <t>0.0019,0.4498,0.9707,0.0005</t>
+  </si>
+  <si>
+    <t>0.0102,0.0028,0.9886,0.0009</t>
+  </si>
+  <si>
+    <t>0.2545,0.6097,0.1073,0.0011</t>
+  </si>
+  <si>
+    <t>0.0727,0.9516,0.0009,0.0001</t>
+  </si>
+  <si>
+    <t>0.9153,0.0373,0.0379,0.0040</t>
+  </si>
+  <si>
+    <t>0.6166,0.1833,0.2820,0.0137</t>
+  </si>
+  <si>
+    <t>0.2038,0.5409,0.1164,0.0008</t>
+  </si>
+  <si>
+    <t>0.0030,0.7497,0.8490,0.0004</t>
+  </si>
+  <si>
+    <t>0.0007,0.9497,0.6836,0.0001</t>
+  </si>
+  <si>
+    <t>0.0023,0.9859,0.0893,0.0004</t>
+  </si>
+  <si>
+    <t>0.0005,0.9620,0.7958,0.0005</t>
+  </si>
+  <si>
+    <t>0.0538,0.0031,0.3704,0.6281</t>
+  </si>
+  <si>
+    <t>0.0035,0.0058,0.0011,0.9975</t>
+  </si>
+  <si>
+    <t>0.0097,0.0089,0.0016,0.9933</t>
+  </si>
+  <si>
+    <t>0.0108,0.0181,0.0022,0.9930</t>
+  </si>
+  <si>
+    <t>0.0429,0.0035,0.0079,0.9709</t>
+  </si>
+  <si>
+    <t>0.0039,0.0212,0.0010,0.9968</t>
+  </si>
+  <si>
+    <t>0.0058,0.9274,0.3461,0.0011</t>
+  </si>
+  <si>
+    <t>0.0059,0.7285,0.9046,0.0017</t>
+  </si>
+  <si>
+    <t>0.0495,0.2843,0.7628,0.0065</t>
+  </si>
+  <si>
+    <t>0.0209,0.1335,0.9348,0.0020</t>
+  </si>
+  <si>
+    <t>0.0006,0.9529,0.6203,0.0000</t>
+  </si>
+  <si>
+    <t>0.0026,0.9648,0.3317,0.0004</t>
+  </si>
+  <si>
+    <t>0.9963,0.0014,0.0003,0.0004</t>
+  </si>
+  <si>
+    <t>0.9829,0.0266,0.0006,0.0002</t>
+  </si>
+  <si>
+    <t>0.9482,0.0667,0.0086,0.0013</t>
+  </si>
+  <si>
+    <t>0.9940,0.0040,0.0006,0.0004</t>
+  </si>
+  <si>
+    <t>0.9873,0.0090,0.0022,0.0006</t>
+  </si>
+  <si>
+    <t>0.9954,0.0021,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.9849,0.0149,0.0019,0.0005</t>
+  </si>
+  <si>
+    <t>0.9893,0.0146,0.0006,0.0001</t>
+  </si>
+  <si>
+    <t>0.9946,0.0042,0.0006,0.0002</t>
+  </si>
+  <si>
+    <t>0.9967,0.0015,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.9967,0.0006,0.0002,0.0007</t>
+  </si>
+  <si>
+    <t>0.9963,0.0013,0.0003,0.0005</t>
+  </si>
+  <si>
+    <t>0.9780,0.0257,0.0026,0.0007</t>
+  </si>
+  <si>
+    <t>0.9982,0.0009,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9957,0.0019,0.0003,0.0004</t>
+  </si>
+  <si>
+    <t>0.9965,0.0013,0.0006,0.0003</t>
+  </si>
+  <si>
+    <t>0.0045,0.0041,0.9763,0.0285</t>
+  </si>
+  <si>
+    <t>0.2924,0.0211,0.7287,0.0043</t>
+  </si>
+  <si>
+    <t>0.4933,0.0116,0.5962,0.0073</t>
+  </si>
+  <si>
+    <t>0.0980,0.0054,0.9157,0.0039</t>
+  </si>
+  <si>
+    <t>0.0756,0.9431,0.0023,0.0002</t>
+  </si>
+  <si>
+    <t>0.0821,0.9333,0.0079,0.0002</t>
+  </si>
+  <si>
+    <t>0.0606,0.9499,0.0021,0.0005</t>
+  </si>
+  <si>
+    <t>0.7330,0.4092,0.0038,0.0007</t>
+  </si>
+  <si>
+    <t>0.1051,0.9290,0.0038,0.0001</t>
+  </si>
+  <si>
+    <t>0.0212,0.9785,0.0015,0.0001</t>
+  </si>
+  <si>
+    <t>0.6713,0.4629,0.0047,0.0007</t>
+  </si>
+  <si>
+    <t>0.5111,0.3033,0.2797,0.0308</t>
+  </si>
+  <si>
+    <t>0.7572,0.0060,0.3408,0.0013</t>
+  </si>
+  <si>
+    <t>0.3065,0.4301,0.3481,0.0146</t>
+  </si>
+  <si>
+    <t>0.4649,0.0141,0.6173,0.0032</t>
+  </si>
+  <si>
+    <t>0.3067,0.5619,0.0763,0.1771</t>
+  </si>
+  <si>
+    <t>0.0090,0.9770,0.0439,0.0012</t>
+  </si>
+  <si>
+    <t>0.0042,0.9857,0.0124,0.0058</t>
+  </si>
+  <si>
+    <t>0.1119,0.8610,0.0224,0.0278</t>
+  </si>
+  <si>
+    <t>0.0019,0.9844,0.1852,0.0027</t>
+  </si>
+  <si>
+    <t>0.0259,0.9689,0.0326,0.0002</t>
+  </si>
+  <si>
+    <t>0.6777,0.4011,0.0216,0.0016</t>
+  </si>
+  <si>
+    <t>0.6566,0.3251,0.0510,0.0014</t>
+  </si>
+  <si>
+    <t>0.9786,0.0131,0.0036,0.0011</t>
+  </si>
+  <si>
+    <t>0.9862,0.0038,0.0023,0.0032</t>
+  </si>
+  <si>
+    <t>0.9803,0.0198,0.0024,0.0007</t>
+  </si>
+  <si>
+    <t>0.9782,0.0105,0.0045,0.0040</t>
+  </si>
+  <si>
+    <t>0.9828,0.0125,0.0013,0.0025</t>
+  </si>
+  <si>
+    <t>0.9743,0.0226,0.0041,0.0009</t>
+  </si>
+  <si>
+    <t>0.9858,0.0116,0.0013,0.0012</t>
+  </si>
+  <si>
+    <t>0.9909,0.0048,0.0026,0.0005</t>
+  </si>
+  <si>
+    <t>0.0023,0.8345,0.7598,0.0002</t>
+  </si>
+  <si>
+    <t>0.0055,0.5704,0.8849,0.0002</t>
+  </si>
+  <si>
+    <t>0.0595,0.1318,0.8831,0.0126</t>
+  </si>
+  <si>
+    <t>0.0668,0.0265,0.9104,0.0061</t>
+  </si>
+  <si>
+    <t>0.6730,0.0708,0.2847,0.0228</t>
+  </si>
+  <si>
+    <t>0.4609,0.3991,0.1015,0.0555</t>
+  </si>
+  <si>
+    <t>0.4899,0.0071,0.6722,0.0026</t>
+  </si>
+  <si>
+    <t>0.7777,0.0378,0.1983,0.0056</t>
+  </si>
+  <si>
+    <t>0.1604,0.0196,0.0311,0.8881</t>
+  </si>
+  <si>
+    <t>0.0040,0.0003,0.0007,0.9975</t>
+  </si>
+  <si>
+    <t>0.0018,0.0029,0.0056,0.9960</t>
+  </si>
+  <si>
+    <t>0.0185,0.0050,0.0024,0.9903</t>
+  </si>
+  <si>
+    <t>0.0208,0.8723,0.4430,0.0034</t>
+  </si>
+  <si>
+    <t>0.9769,0.0208,0.0050,0.0006</t>
+  </si>
+  <si>
+    <t>0.2558,0.7818,0.0129,0.0066</t>
+  </si>
+  <si>
+    <t>0.9863,0.0092,0.0008,0.0016</t>
+  </si>
+  <si>
+    <t>0.8911,0.1888,0.0038,0.0003</t>
+  </si>
+  <si>
+    <t>0.9265,0.0360,0.0128,0.0195</t>
+  </si>
+  <si>
+    <t>0.4153,0.3076,0.0737,0.3925</t>
+  </si>
+  <si>
+    <t>0.9597,0.0344,0.0067,0.0023</t>
+  </si>
+  <si>
+    <t>0.0295,0.1561,0.9169,0.0415</t>
+  </si>
+  <si>
+    <t>0.8771,0.0029,0.0458,0.0375</t>
+  </si>
+  <si>
+    <t>0.9736,0.0041,0.0010,0.0112</t>
+  </si>
+  <si>
+    <t>0.5347,0.5243,0.0247,0.0060</t>
+  </si>
+  <si>
+    <t>0.6748,0.2617,0.1006,0.0026</t>
+  </si>
+  <si>
+    <t>0.8255,0.1782,0.0312,0.0029</t>
+  </si>
+  <si>
+    <t>0.2435,0.7297,0.0371,0.0304</t>
+  </si>
+  <si>
+    <t>0.8626,0.0581,0.0732,0.0013</t>
+  </si>
+  <si>
+    <t>0.8389,0.0535,0.1127,0.0228</t>
+  </si>
+  <si>
+    <t>0.9860,0.0087,0.0027,0.0009</t>
+  </si>
+  <si>
+    <t>0.9875,0.0049,0.0008,0.0026</t>
+  </si>
+  <si>
+    <t>0.9884,0.0050,0.0015,0.0014</t>
+  </si>
+  <si>
+    <t>0.9843,0.0048,0.0038,0.0020</t>
+  </si>
+  <si>
+    <t>0.9857,0.0086,0.0019,0.0017</t>
+  </si>
+  <si>
+    <t>0.9919,0.0081,0.0005,0.0002</t>
+  </si>
+  <si>
+    <t>0.9878,0.0065,0.0011,0.0021</t>
+  </si>
+  <si>
+    <t>0.9709,0.0161,0.0038,0.0044</t>
+  </si>
+  <si>
+    <t>0.5871,0.5412,0.0094,0.0015</t>
+  </si>
+  <si>
+    <t>0.8692,0.2242,0.0055,0.0004</t>
+  </si>
+  <si>
+    <t>0.7400,0.3081,0.0197,0.0003</t>
+  </si>
+  <si>
+    <t>0.0916,0.2598,0.8111,0.0041</t>
+  </si>
+  <si>
+    <t>0.9699,0.0348,0.0031,0.0006</t>
+  </si>
+  <si>
+    <t>0.9298,0.0605,0.0112,0.0076</t>
+  </si>
+  <si>
+    <t>0.9079,0.1690,0.0032,0.0003</t>
+  </si>
+  <si>
+    <t>0.9437,0.0599,0.0091,0.0013</t>
+  </si>
+  <si>
+    <t>0.0178,0.0746,0.9709,0.0030</t>
+  </si>
+  <si>
+    <t>0.9319,0.0840,0.0109,0.0008</t>
+  </si>
+  <si>
+    <t>0.0312,0.0062,0.9756,0.0011</t>
+  </si>
+  <si>
+    <t>0.0260,0.0554,0.9466,0.0108</t>
+  </si>
+  <si>
+    <t>0.1962,0.0065,0.8742,0.0017</t>
+  </si>
+  <si>
+    <t>0.0281,0.1323,0.9362,0.0016</t>
+  </si>
+  <si>
+    <t>0.0470,0.0055,0.9581,0.0022</t>
+  </si>
+  <si>
+    <t>0.0179,0.0006,0.9905,0.0002</t>
+  </si>
+  <si>
+    <t>0.0044,0.0067,0.9930,0.0007</t>
+  </si>
+  <si>
+    <t>0.2298,0.0096,0.8256,0.0042</t>
+  </si>
+  <si>
+    <t>0.3338,0.0030,0.8286,0.0008</t>
+  </si>
+  <si>
+    <t>0.1711,0.0735,0.7535,0.0323</t>
+  </si>
+  <si>
+    <t>0.8154,0.0148,0.2060,0.0020</t>
+  </si>
+  <si>
+    <t>0.3396,0.2394,0.4064,0.0038</t>
+  </si>
+  <si>
+    <t>0.5862,0.0392,0.4327,0.0074</t>
+  </si>
+  <si>
+    <t>0.4384,0.0492,0.5400,0.0125</t>
+  </si>
+  <si>
+    <t>0.5530,0.2233,0.3209,0.0264</t>
+  </si>
+  <si>
+    <t>0.8312,0.2885,0.0060,0.0007</t>
+  </si>
+  <si>
+    <t>0.4579,0.7432,0.0011,0.0001</t>
+  </si>
+  <si>
+    <t>0.7806,0.3598,0.0036,0.0001</t>
+  </si>
+  <si>
+    <t>0.9856,0.0160,0.0014,0.0003</t>
+  </si>
+  <si>
+    <t>0.8915,0.1847,0.0050,0.0007</t>
+  </si>
+  <si>
+    <t>0.3505,0.4406,0.2477,0.0173</t>
+  </si>
+  <si>
+    <t>0.7113,0.0156,0.2581,0.0234</t>
+  </si>
+  <si>
+    <t>0.6488,0.0328,0.2921,0.0542</t>
+  </si>
+  <si>
+    <t>0.7452,0.0083,0.3583,0.0018</t>
+  </si>
+  <si>
+    <t>0.4125,0.1271,0.4786,0.0103</t>
+  </si>
+  <si>
+    <t>0.0204,0.0072,0.9492,0.0333</t>
+  </si>
+  <si>
+    <t>0.0359,0.3040,0.8253,0.0069</t>
+  </si>
+  <si>
+    <t>0.0213,0.0747,0.8418,0.1372</t>
+  </si>
+  <si>
+    <t>0.0712,0.1101,0.8545,0.0039</t>
+  </si>
+  <si>
+    <t>0.0190,0.2763,0.8857,0.0023</t>
+  </si>
+  <si>
+    <t>0.9849,0.0097,0.0008,0.0018</t>
+  </si>
+  <si>
+    <t>0.9873,0.0093,0.0036,0.0003</t>
+  </si>
+  <si>
+    <t>0.9325,0.1059,0.0032,0.0008</t>
+  </si>
+  <si>
+    <t>0.9921,0.0084,0.0008,0.0002</t>
+  </si>
+  <si>
+    <t>0.9922,0.0058,0.0012,0.0003</t>
+  </si>
+  <si>
+    <t>0.9796,0.0172,0.0027,0.0013</t>
+  </si>
+  <si>
+    <t>0.9929,0.0040,0.0008,0.0006</t>
+  </si>
+  <si>
+    <t>0.9935,0.0039,0.0010,0.0003</t>
+  </si>
+  <si>
+    <t>0.0201,0.0196,0.9704,0.0049</t>
+  </si>
+  <si>
+    <t>0.4953,0.2945,0.2689,0.0040</t>
+  </si>
+  <si>
+    <t>0.7970,0.0249,0.1681,0.0215</t>
+  </si>
+  <si>
+    <t>0.0332,0.0055,0.9734,0.0017</t>
+  </si>
+  <si>
+    <t>0.0035,0.0195,0.9859,0.0029</t>
+  </si>
+  <si>
+    <t>0.0090,0.0174,0.9865,0.0009</t>
+  </si>
+  <si>
+    <t>0.0061,0.0034,0.9919,0.0011</t>
+  </si>
+  <si>
+    <t>0.2012,0.0086,0.8489,0.0010</t>
+  </si>
+  <si>
+    <t>0.0047,0.0403,0.9830,0.0040</t>
+  </si>
+  <si>
+    <t>0.0652,0.0029,0.9592,0.0005</t>
+  </si>
+  <si>
+    <t>0.0083,0.1451,0.9568,0.0008</t>
+  </si>
+  <si>
+    <t>0.5489,0.0093,0.5273,0.0152</t>
+  </si>
+  <si>
+    <t>0.7515,0.0088,0.3191,0.0022</t>
+  </si>
+  <si>
+    <t>0.8535,0.0121,0.1197,0.0080</t>
+  </si>
+  <si>
+    <t>0.9940,0.0025,0.0005,0.0004</t>
+  </si>
+  <si>
+    <t>0.9934,0.0054,0.0009,0.0002</t>
+  </si>
+  <si>
+    <t>0.9943,0.0060,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.7309,0.3474,0.0113,0.0002</t>
+  </si>
+  <si>
+    <t>0.9941,0.0020,0.0006,0.0010</t>
+  </si>
+  <si>
+    <t>0.9868,0.0110,0.0017,0.0007</t>
+  </si>
+  <si>
+    <t>0.9867,0.0230,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.9869,0.0098,0.0010,0.0008</t>
+  </si>
+  <si>
+    <t>0.1281,0.2016,0.6231,0.0128</t>
+  </si>
+  <si>
+    <t>0.0029,0.0099,0.9928,0.0019</t>
+  </si>
+  <si>
+    <t>0.0186,0.0374,0.9581,0.0056</t>
+  </si>
+  <si>
+    <t>0.2492,0.0658,0.6865,0.0088</t>
+  </si>
+  <si>
+    <t>0.0088,0.0178,0.9723,0.0117</t>
+  </si>
+  <si>
+    <t>0.2292,0.0899,0.5390,0.2936</t>
+  </si>
+  <si>
+    <t>0.2749,0.0127,0.7520,0.0299</t>
+  </si>
+  <si>
+    <t>0.0825,0.1000,0.8371,0.0650</t>
+  </si>
+  <si>
+    <t>0.6573,0.0072,0.0245,0.3134</t>
+  </si>
+  <si>
+    <t>0.1609,0.0199,0.0087,0.9283</t>
+  </si>
+  <si>
+    <t>0.0946,0.0039,0.0032,0.9558</t>
+  </si>
+  <si>
+    <t>0.0040,0.0028,0.0002,0.9979</t>
+  </si>
+  <si>
+    <t>0.0160,0.0003,0.0006,0.9929</t>
+  </si>
+  <si>
+    <t>0.6423,0.0586,0.0531,0.3506</t>
   </si>
 </sst>
 </file>
@@ -1959,7 +1968,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1973,7 +1982,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1987,7 +1996,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2001,7 +2010,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2015,7 +2024,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2029,7 +2038,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2043,7 +2052,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2057,7 +2066,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2071,7 +2080,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2085,7 +2094,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2099,7 +2108,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2113,7 +2122,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2127,7 +2136,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2141,7 +2150,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2152,10 +2161,10 @@
         <v>261</v>
       </c>
       <c r="C16" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D16" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2169,7 +2178,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2183,7 +2192,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2197,7 +2206,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2211,7 +2220,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2225,7 +2234,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2239,7 +2248,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2253,7 +2262,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2267,7 +2276,7 @@
         <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2281,7 +2290,7 @@
         <v>261</v>
       </c>
       <c r="D25" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2295,7 +2304,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2309,7 +2318,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2323,7 +2332,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2337,7 +2346,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2351,7 +2360,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2362,10 +2371,10 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2379,7 +2388,7 @@
         <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2393,7 +2402,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2407,7 +2416,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2418,10 +2427,10 @@
         <v>259</v>
       </c>
       <c r="C35" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D35" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2435,7 +2444,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2446,10 +2455,10 @@
         <v>259</v>
       </c>
       <c r="C37" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D37" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2463,7 +2472,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2474,10 +2483,10 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D39" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2491,7 +2500,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2502,10 +2511,10 @@
         <v>261</v>
       </c>
       <c r="C41" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D41" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2519,7 +2528,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2533,7 +2542,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2547,7 +2556,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2561,7 +2570,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2572,10 +2581,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D46" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2589,7 +2598,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2603,7 +2612,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2617,7 +2626,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2628,10 +2637,10 @@
         <v>261</v>
       </c>
       <c r="C50" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D50" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2645,7 +2654,7 @@
         <v>263</v>
       </c>
       <c r="D51" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2659,7 +2668,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2673,7 +2682,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2687,7 +2696,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2701,7 +2710,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2715,7 +2724,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2729,7 +2738,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2743,7 +2752,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2757,7 +2766,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2771,7 +2780,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2785,7 +2794,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2799,7 +2808,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2813,7 +2822,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2827,7 +2836,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2841,7 +2850,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2852,10 +2861,10 @@
         <v>263</v>
       </c>
       <c r="C66" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D66" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2869,7 +2878,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2883,7 +2892,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2897,7 +2906,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2911,7 +2920,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2925,7 +2934,7 @@
         <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2936,10 +2945,10 @@
         <v>261</v>
       </c>
       <c r="C72" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D72" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2953,7 +2962,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2967,7 +2976,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2981,7 +2990,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2995,7 +3004,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3009,7 +3018,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3023,7 +3032,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3037,7 +3046,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3051,7 +3060,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3065,7 +3074,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3079,7 +3088,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3090,10 +3099,10 @@
         <v>263</v>
       </c>
       <c r="C83" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D83" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3107,7 +3116,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3121,7 +3130,7 @@
         <v>261</v>
       </c>
       <c r="D85" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3132,10 +3141,10 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D86" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3146,10 +3155,10 @@
         <v>263</v>
       </c>
       <c r="C87" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3160,10 +3169,10 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D88" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3177,7 +3186,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3191,7 +3200,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3205,7 +3214,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3219,7 +3228,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3233,7 +3242,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3247,7 +3256,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3261,7 +3270,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3275,7 +3284,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3289,7 +3298,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3303,7 +3312,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3317,7 +3326,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3331,7 +3340,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3345,7 +3354,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3359,7 +3368,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3373,7 +3382,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3387,7 +3396,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3401,7 +3410,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3415,7 +3424,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3426,10 +3435,10 @@
         <v>259</v>
       </c>
       <c r="C107" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D107" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3443,7 +3452,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3457,7 +3466,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3471,7 +3480,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3485,7 +3494,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3496,10 +3505,10 @@
         <v>262</v>
       </c>
       <c r="C112" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D112" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3513,7 +3522,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3527,7 +3536,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3541,7 +3550,7 @@
         <v>259</v>
       </c>
       <c r="D115" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3555,7 +3564,7 @@
         <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3566,10 +3575,10 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D117" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3580,10 +3589,10 @@
         <v>259</v>
       </c>
       <c r="C118" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="D118" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3594,10 +3603,10 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D119" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3608,10 +3617,10 @@
         <v>262</v>
       </c>
       <c r="C120" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D120" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3625,7 +3634,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3639,7 +3648,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3653,7 +3662,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3664,10 +3673,10 @@
         <v>263</v>
       </c>
       <c r="C124" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D124" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3681,7 +3690,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3695,7 +3704,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3706,10 +3715,10 @@
         <v>259</v>
       </c>
       <c r="C127" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3723,7 +3732,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3737,7 +3746,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3751,7 +3760,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3765,7 +3774,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3779,7 +3788,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3793,7 +3802,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3807,7 +3816,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3821,7 +3830,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3835,7 +3844,7 @@
         <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3849,7 +3858,7 @@
         <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3863,7 +3872,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3877,7 +3886,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3891,7 +3900,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3902,10 +3911,10 @@
         <v>259</v>
       </c>
       <c r="C141" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="D141" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3916,10 +3925,10 @@
         <v>261</v>
       </c>
       <c r="C142" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3933,7 +3942,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3947,7 +3956,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3961,7 +3970,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3975,7 +3984,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3989,7 +3998,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4003,7 +4012,7 @@
         <v>262</v>
       </c>
       <c r="D148" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4017,7 +4026,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4031,7 +4040,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4045,7 +4054,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4056,10 +4065,10 @@
         <v>262</v>
       </c>
       <c r="C152" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D152" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4073,7 +4082,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4084,10 +4093,10 @@
         <v>259</v>
       </c>
       <c r="C154" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="D154" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4101,7 +4110,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4115,7 +4124,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4129,7 +4138,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4143,7 +4152,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4154,10 +4163,10 @@
         <v>259</v>
       </c>
       <c r="C159" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="D159" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4171,7 +4180,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4185,7 +4194,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4196,10 +4205,10 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D162" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4213,7 +4222,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4227,7 +4236,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4241,7 +4250,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4255,7 +4264,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4269,7 +4278,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4283,7 +4292,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4297,7 +4306,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4311,7 +4320,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4325,7 +4334,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4339,7 +4348,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4350,10 +4359,10 @@
         <v>259</v>
       </c>
       <c r="C173" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="D173" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4367,7 +4376,7 @@
         <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4381,7 +4390,7 @@
         <v>259</v>
       </c>
       <c r="D175" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4392,10 +4401,10 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D176" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4409,7 +4418,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4423,7 +4432,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4437,7 +4446,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4451,7 +4460,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4465,7 +4474,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4479,7 +4488,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4493,7 +4502,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4507,7 +4516,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4521,7 +4530,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4535,7 +4544,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4549,7 +4558,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4563,7 +4572,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4577,7 +4586,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4588,10 +4597,10 @@
         <v>259</v>
       </c>
       <c r="C190" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4605,7 +4614,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4616,10 +4625,10 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4633,7 +4642,7 @@
         <v>259</v>
       </c>
       <c r="D193" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4644,10 +4653,10 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="D194" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4661,7 +4670,7 @@
         <v>259</v>
       </c>
       <c r="D195" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4675,7 +4684,7 @@
         <v>261</v>
       </c>
       <c r="D196" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4686,10 +4695,10 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D197" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4703,7 +4712,7 @@
         <v>259</v>
       </c>
       <c r="D198" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4717,7 +4726,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4731,7 +4740,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4745,7 +4754,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4759,7 +4768,7 @@
         <v>259</v>
       </c>
       <c r="D202" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4770,10 +4779,10 @@
         <v>259</v>
       </c>
       <c r="C203" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="D203" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4787,7 +4796,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4801,7 +4810,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4815,7 +4824,7 @@
         <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4826,10 +4835,10 @@
         <v>259</v>
       </c>
       <c r="C207" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="D207" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4843,7 +4852,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4857,7 +4866,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4871,7 +4880,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4885,7 +4894,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4899,7 +4908,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4913,7 +4922,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4927,7 +4936,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4941,7 +4950,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4955,7 +4964,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4969,7 +4978,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4983,7 +4992,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4997,7 +5006,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5011,7 +5020,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5025,7 +5034,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5036,10 +5045,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="D222" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5053,7 +5062,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5067,7 +5076,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5081,7 +5090,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5095,7 +5104,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5109,7 +5118,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5123,7 +5132,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5137,7 +5146,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5151,7 +5160,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5165,7 +5174,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5176,10 +5185,10 @@
         <v>259</v>
       </c>
       <c r="C232" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D232" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5193,7 +5202,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5207,7 +5216,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5221,7 +5230,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5235,7 +5244,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5249,7 +5258,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5263,7 +5272,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5277,7 +5286,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5291,7 +5300,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5305,7 +5314,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5319,7 +5328,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5333,7 +5342,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5347,7 +5356,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5361,7 +5370,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5375,7 +5384,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5389,7 +5398,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5403,7 +5412,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5417,7 +5426,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5431,7 +5440,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5445,7 +5454,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5459,7 +5468,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5473,7 +5482,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5487,7 +5496,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5501,7 +5510,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5515,7 +5524,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
     </row>
   </sheetData>
